--- a/output/coefficients/standardized/standardized_NA.xlsx
+++ b/output/coefficients/standardized/standardized_NA.xlsx
@@ -460,15 +460,15 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2777986468582379</v>
+        <v>0.2778</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009045722481464413</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>30.71049851766678</v>
+        <v>30.7105</v>
       </c>
       <c r="G2" t="n">
         <v>4.121846448096214e-207</v>
@@ -481,19 +481,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07839545140456043</v>
+        <v>0.0784</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003855048023438303</v>
+        <v>0.0039</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2573863037393153</v>
+        <v>0.2574</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0126568129108651</v>
+        <v>0.0127</v>
       </c>
       <c r="F3" t="n">
-        <v>20.33579113098566</v>
+        <v>20.3358</v>
       </c>
       <c r="G3" t="n">
         <v>6.203109040878432e-92</v>
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1548845476955757</v>
+        <v>-0.1549</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005913038048582205</v>
+        <v>0.0059</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2965496231808294</v>
+        <v>-0.2965</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01132139539579809</v>
+        <v>0.0113</v>
       </c>
       <c r="F4" t="n">
-        <v>-26.19373432455978</v>
+        <v>-26.1937</v>
       </c>
       <c r="G4" t="n">
         <v>3.13217078813274e-151</v>
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.001315990753542443</v>
+        <v>-0.0013</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000465485405620212</v>
+        <v>0.0005</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.02598201546251751</v>
+        <v>-0.026</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009190223391649778</v>
+        <v>0.0092</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.827136442202779</v>
+        <v>-2.8271</v>
       </c>
       <c r="G5" t="n">
         <v>0.004696631178074946</v>
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0632990336894094</v>
+        <v>0.0633</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00923940306674109</v>
+        <v>0.0092</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09855164103476707</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01438502740621363</v>
+        <v>0.0144</v>
       </c>
       <c r="F6" t="n">
-        <v>6.850987367059</v>
+        <v>6.851</v>
       </c>
       <c r="G6" t="n">
         <v>7.334199362201158e-12</v>
@@ -581,19 +581,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08066712117979756</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009466039941280693</v>
+        <v>0.0095</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1208146849730236</v>
+        <v>0.1208</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01417723375672294</v>
+        <v>0.0142</v>
       </c>
       <c r="F7" t="n">
-        <v>8.521738940484951</v>
+        <v>8.521699999999999</v>
       </c>
       <c r="G7" t="n">
         <v>1.571753521963822e-17</v>
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07723327199807399</v>
+        <v>0.0772</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009720868605305385</v>
+        <v>0.0097</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09607930905177713</v>
+        <v>0.0961</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01209290134702755</v>
+        <v>0.0121</v>
       </c>
       <c r="F8" t="n">
-        <v>7.94509988088124</v>
+        <v>7.9451</v>
       </c>
       <c r="G8" t="n">
         <v>1.940343772614067e-15</v>
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03430475571610891</v>
+        <v>0.0343</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009595090718052772</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03576095157738726</v>
+        <v>0.0358</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0100023908459956</v>
+        <v>0.01</v>
       </c>
       <c r="F9" t="n">
-        <v>3.575240372825857</v>
+        <v>3.5752</v>
       </c>
       <c r="G9" t="n">
         <v>0.0003499062625434746</v>
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1111827367386595</v>
+        <v>0.1112</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0126135091700904</v>
+        <v>0.0126</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1356695076578593</v>
+        <v>0.1357</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01539149538085647</v>
+        <v>0.0154</v>
       </c>
       <c r="F10" t="n">
-        <v>8.814576121472996</v>
+        <v>8.8146</v>
       </c>
       <c r="G10" t="n">
         <v>1.201387264815336e-18</v>
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02443124612557207</v>
+        <v>0.0244</v>
       </c>
       <c r="C11" t="n">
-        <v>0.009557662671892266</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02943995140631993</v>
+        <v>0.0294</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01151710081312595</v>
+        <v>0.0115</v>
       </c>
       <c r="F11" t="n">
-        <v>2.556194643426882</v>
+        <v>2.5562</v>
       </c>
       <c r="G11" t="n">
         <v>0.01058239055606917</v>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07756457838091581</v>
+        <v>0.0776</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01107869663848694</v>
+        <v>0.0111</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0748063070607778</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01068472748606818</v>
+        <v>0.0107</v>
       </c>
       <c r="F12" t="n">
-        <v>7.001236780097365</v>
+        <v>7.0012</v>
       </c>
       <c r="G12" t="n">
         <v>2.537127339931194e-12</v>
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03851234493399321</v>
+        <v>0.0385</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0100209068257704</v>
+        <v>0.01</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0390369970610609</v>
+        <v>0.039</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01015742123667679</v>
+        <v>0.0102</v>
       </c>
       <c r="F13" t="n">
-        <v>3.843199582991075</v>
+        <v>3.8432</v>
       </c>
       <c r="G13" t="n">
         <v>0.0001214406303753483</v>
@@ -756,19 +756,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05608239709869824</v>
+        <v>0.0561</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01177342940935744</v>
+        <v>0.0118</v>
       </c>
       <c r="D14" t="n">
-        <v>0.04713653148156568</v>
+        <v>0.0471</v>
       </c>
       <c r="E14" t="n">
-        <v>0.009895415579749701</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>4.763471640142876</v>
+        <v>4.7635</v>
       </c>
       <c r="G14" t="n">
         <v>1.902903654966833e-06</v>
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.02742887116376902</v>
+        <v>-0.0274</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01057591723238545</v>
+        <v>0.0106</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.01874368335421085</v>
+        <v>-0.0187</v>
       </c>
       <c r="E15" t="n">
-        <v>0.007227116369485166</v>
+        <v>0.0072</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.593521730652038</v>
+        <v>-2.5935</v>
       </c>
       <c r="G15" t="n">
         <v>0.009499853553076362</v>
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.005010339418654501</v>
+        <v>0.005</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0101869734449156</v>
+        <v>0.0102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.003927189110710777</v>
+        <v>0.0039</v>
       </c>
       <c r="E16" t="n">
-        <v>0.007984722758506415</v>
+        <v>0.008</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4918378795966334</v>
+        <v>0.4918</v>
       </c>
       <c r="G16" t="n">
         <v>0.6228339559200247</v>
@@ -831,19 +831,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06597891720411807</v>
+        <v>0.066</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01868459494621359</v>
+        <v>0.0187</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0372164344452271</v>
+        <v>0.0372</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01053933638832099</v>
+        <v>0.0105</v>
       </c>
       <c r="F17" t="n">
-        <v>3.531193338365016</v>
+        <v>3.5312</v>
       </c>
       <c r="G17" t="n">
         <v>0.0004136892471294721</v>
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.07422412464631249</v>
+        <v>0.0742</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0253455807765246</v>
+        <v>0.0253</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02774863339095885</v>
+        <v>0.0277</v>
       </c>
       <c r="E18" t="n">
-        <v>0.009475426384616258</v>
+        <v>0.0095</v>
       </c>
       <c r="F18" t="n">
-        <v>2.92848387656833</v>
+        <v>2.9285</v>
       </c>
       <c r="G18" t="n">
         <v>0.003406194983078177</v>
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.03231082833638427</v>
+        <v>0.0323</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02267244677812823</v>
+        <v>0.0227</v>
       </c>
       <c r="D19" t="n">
-        <v>0.008785027514731489</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.006164437095159622</v>
+        <v>0.0062</v>
       </c>
       <c r="F19" t="n">
-        <v>1.425114309566007</v>
+        <v>1.4251</v>
       </c>
       <c r="G19" t="n">
         <v>0.1541241609055243</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06124395690136044</v>
+        <v>-0.0612</v>
       </c>
       <c r="C20" t="n">
-        <v>0.005186959996277839</v>
+        <v>0.0052</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1073858247555929</v>
+        <v>-0.1074</v>
       </c>
       <c r="E20" t="n">
-        <v>0.009094872463444467</v>
+        <v>0.0091</v>
       </c>
       <c r="F20" t="n">
-        <v>-11.80729308599046</v>
+        <v>-11.8073</v>
       </c>
       <c r="G20" t="n">
         <v>3.578989638699906e-32</v>
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.0435226201930169</v>
+        <v>-0.0435</v>
       </c>
       <c r="C21" t="n">
-        <v>0.006012887130669324</v>
+        <v>0.006</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.06562345209408321</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.009066237483328689</v>
+        <v>0.0091</v>
       </c>
       <c r="F21" t="n">
-        <v>-7.23822337709043</v>
+        <v>-7.2382</v>
       </c>
       <c r="G21" t="n">
         <v>4.546002757444119e-13</v>
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1572942281385584</v>
+        <v>-0.1573</v>
       </c>
       <c r="C22" t="n">
-        <v>0.01197350538976417</v>
+        <v>0.012</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1115202358532186</v>
+        <v>-0.1115</v>
       </c>
       <c r="E22" t="n">
-        <v>0.008489110890197748</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-13.1368570037163</v>
+        <v>-13.1369</v>
       </c>
       <c r="G22" t="n">
         <v>2.024629328319839e-39</v>
@@ -981,19 +981,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.008906718157930458</v>
+        <v>0.0089</v>
       </c>
       <c r="C23" t="n">
-        <v>0.006728659038823263</v>
+        <v>0.0067</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01514732354565864</v>
+        <v>0.0151</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01144317959569954</v>
+        <v>0.0114</v>
       </c>
       <c r="F23" t="n">
-        <v>1.323698839031693</v>
+        <v>1.3237</v>
       </c>
       <c r="G23" t="n">
         <v>0.1856030841934638</v>
@@ -1006,19 +1006,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1039332756087135</v>
+        <v>-0.1039</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00650955666450826</v>
+        <v>0.0065</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1057551060924098</v>
+        <v>-0.1058</v>
       </c>
       <c r="E24" t="n">
-        <v>0.006623661687151804</v>
+        <v>0.0066</v>
       </c>
       <c r="F24" t="n">
-        <v>-15.96626021790145</v>
+        <v>-15.9663</v>
       </c>
       <c r="G24" t="n">
         <v>2.195617844741011e-57</v>

--- a/output/coefficients/standardized/standardized_NA.xlsx
+++ b/output/coefficients/standardized/standardized_NA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,18 +460,18 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2778</v>
+        <v>0.2985</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0091</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>30.7105</v>
+        <v>32.7004</v>
       </c>
       <c r="G2" t="n">
-        <v>4.121846448096214e-207</v>
+        <v>1.543351766214401e-234</v>
       </c>
     </row>
     <row r="3">
@@ -481,22 +481,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0784</v>
+        <v>0.0756</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0039</v>
+        <v>0.0038</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2574</v>
+        <v>0.2483</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0127</v>
+        <v>0.0126</v>
       </c>
       <c r="F3" t="n">
-        <v>20.3358</v>
+        <v>19.645</v>
       </c>
       <c r="G3" t="n">
-        <v>6.203109040878432e-92</v>
+        <v>6.379495164655918e-86</v>
       </c>
     </row>
     <row r="4">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1549</v>
+        <v>-0.1424</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0059</v>
+        <v>0.006</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2965</v>
+        <v>-0.2726</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0113</v>
+        <v>0.0114</v>
       </c>
       <c r="F4" t="n">
-        <v>-26.1937</v>
+        <v>-23.8748</v>
       </c>
       <c r="G4" t="n">
-        <v>3.13217078813274e-151</v>
+        <v>5.600838401538451e-126</v>
       </c>
     </row>
     <row r="5">
@@ -531,22 +531,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0017</v>
       </c>
       <c r="C5" t="n">
         <v>0.0005</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.026</v>
+        <v>-0.0341</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0092</v>
+        <v>0.0091</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8271</v>
+        <v>-3.7688</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004696631178074946</v>
+        <v>0.0001640347282356813</v>
       </c>
     </row>
     <row r="6">
@@ -556,22 +556,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0633</v>
+        <v>0.0548</v>
       </c>
       <c r="C6" t="n">
         <v>0.0092</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0852</v>
       </c>
       <c r="E6" t="n">
         <v>0.0144</v>
       </c>
       <c r="F6" t="n">
-        <v>6.851</v>
+        <v>5.9339</v>
       </c>
       <c r="G6" t="n">
-        <v>7.334199362201158e-12</v>
+        <v>2.957447492894423e-09</v>
       </c>
     </row>
     <row r="7">
@@ -581,22 +581,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0634</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0095</v>
+        <v>0.0094</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1208</v>
+        <v>0.0949</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0142</v>
+        <v>0.0141</v>
       </c>
       <c r="F7" t="n">
-        <v>8.521699999999999</v>
+        <v>6.7219</v>
       </c>
       <c r="G7" t="n">
-        <v>1.571753521963822e-17</v>
+        <v>1.79366847143131e-11</v>
       </c>
     </row>
     <row r="8">
@@ -606,22 +606,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0772</v>
+        <v>0.0732</v>
       </c>
       <c r="C8" t="n">
         <v>0.0097</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0961</v>
+        <v>0.0911</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0121</v>
+        <v>0.012</v>
       </c>
       <c r="F8" t="n">
-        <v>7.9451</v>
+        <v>7.5619</v>
       </c>
       <c r="G8" t="n">
-        <v>1.940343772614067e-15</v>
+        <v>3.972147382998328e-14</v>
       </c>
     </row>
     <row r="9">
@@ -631,22 +631,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0343</v>
+        <v>0.0348</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0095</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0358</v>
+        <v>0.0363</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5752</v>
+        <v>3.6551</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0003499062625434746</v>
+        <v>0.0002570401520009639</v>
       </c>
     </row>
     <row r="10">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1112</v>
+        <v>0.1057</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0126</v>
+        <v>0.0124</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1357</v>
+        <v>0.129</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0154</v>
+        <v>0.0151</v>
       </c>
       <c r="F10" t="n">
-        <v>8.8146</v>
+        <v>8.5166</v>
       </c>
       <c r="G10" t="n">
-        <v>1.201387264815336e-18</v>
+        <v>1.643557135152196e-17</v>
       </c>
     </row>
     <row r="11">
@@ -681,22 +681,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0244</v>
+        <v>0.0255</v>
       </c>
       <c r="C11" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0095</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0294</v>
+        <v>0.0308</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0115</v>
+        <v>0.0114</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5562</v>
+        <v>2.7004</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01058239055606917</v>
+        <v>0.006924581632716168</v>
       </c>
     </row>
     <row r="12">
@@ -706,22 +706,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0776</v>
+        <v>0.0697</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0111</v>
+        <v>0.0108</v>
       </c>
       <c r="D12" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0672</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0107</v>
+        <v>0.0104</v>
       </c>
       <c r="F12" t="n">
-        <v>7.0012</v>
+        <v>6.4358</v>
       </c>
       <c r="G12" t="n">
-        <v>2.537127339931194e-12</v>
+        <v>1.228204934607188e-10</v>
       </c>
     </row>
     <row r="13">
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0385</v>
+        <v>0.0309</v>
       </c>
       <c r="C13" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0314</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.01</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.0102</v>
-      </c>
       <c r="F13" t="n">
-        <v>3.8432</v>
+        <v>3.1219</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0001214406303753483</v>
+        <v>0.001796715394070818</v>
       </c>
     </row>
     <row r="14">
@@ -756,22 +756,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0561</v>
+        <v>0.0555</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0118</v>
+        <v>0.0116</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0471</v>
+        <v>0.0466</v>
       </c>
       <c r="E14" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0098</v>
       </c>
       <c r="F14" t="n">
-        <v>4.7635</v>
+        <v>4.7745</v>
       </c>
       <c r="G14" t="n">
-        <v>1.902903654966833e-06</v>
+        <v>1.801970706125262e-06</v>
       </c>
     </row>
     <row r="15">
@@ -781,22 +781,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.0274</v>
+        <v>-0.0307</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0106</v>
+        <v>0.0105</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0187</v>
+        <v>-0.021</v>
       </c>
       <c r="E15" t="n">
         <v>0.0072</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5935</v>
+        <v>-2.9153</v>
       </c>
       <c r="G15" t="n">
-        <v>0.009499853553076362</v>
+        <v>0.003553300905034483</v>
       </c>
     </row>
     <row r="16">
@@ -806,22 +806,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.005</v>
+        <v>0.0171</v>
       </c>
       <c r="C16" t="n">
         <v>0.0102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0039</v>
+        <v>0.0134</v>
       </c>
       <c r="E16" t="n">
         <v>0.008</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4918</v>
+        <v>1.6731</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6228339559200247</v>
+        <v>0.09430899476652224</v>
       </c>
     </row>
     <row r="17">
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.066</v>
+        <v>0.051</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0187</v>
+        <v>0.0185</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0372</v>
+        <v>0.0288</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0105</v>
+        <v>0.0104</v>
       </c>
       <c r="F17" t="n">
-        <v>3.5312</v>
+        <v>2.7568</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004136892471294721</v>
+        <v>0.005836821367813983</v>
       </c>
     </row>
     <row r="18">
@@ -856,22 +856,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0742</v>
+        <v>0.0553</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0253</v>
+        <v>0.025</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0277</v>
+        <v>0.0207</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0095</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>2.9285</v>
+        <v>2.2126</v>
       </c>
       <c r="G18" t="n">
-        <v>0.003406194983078177</v>
+        <v>0.02692379429928699</v>
       </c>
     </row>
     <row r="19">
@@ -881,22 +881,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0323</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0227</v>
+        <v>0.0228</v>
       </c>
       <c r="D19" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0024</v>
       </c>
       <c r="E19" t="n">
         <v>0.0062</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4251</v>
+        <v>0.3923</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1541241609055243</v>
+        <v>0.6948626568191176</v>
       </c>
     </row>
     <row r="20">
@@ -906,22 +906,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0612</v>
+        <v>-0.0504</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0052</v>
+        <v>0.0051</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1074</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0091</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-11.8073</v>
+        <v>-9.8391</v>
       </c>
       <c r="G20" t="n">
-        <v>3.578989638699906e-32</v>
+        <v>7.639268626007967e-23</v>
       </c>
     </row>
     <row r="21">
@@ -931,22 +931,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.0435</v>
+        <v>-0.0358</v>
       </c>
       <c r="C21" t="n">
-        <v>0.006</v>
+        <v>0.0059</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.054</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0091</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-7.2382</v>
+        <v>-6.0283</v>
       </c>
       <c r="G21" t="n">
-        <v>4.546002757444119e-13</v>
+        <v>1.657370377219674e-09</v>
       </c>
     </row>
     <row r="22">
@@ -956,22 +956,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1573</v>
+        <v>-0.1594</v>
       </c>
       <c r="C22" t="n">
-        <v>0.012</v>
+        <v>0.0119</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1115</v>
+        <v>-0.113</v>
       </c>
       <c r="E22" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-13.1369</v>
+        <v>-13.3933</v>
       </c>
       <c r="G22" t="n">
-        <v>2.024629328319839e-39</v>
+        <v>6.61841632152771e-41</v>
       </c>
     </row>
     <row r="23">
@@ -981,22 +981,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0089</v>
+        <v>0.0062</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0067</v>
+        <v>0.0066</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0151</v>
+        <v>0.0106</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0114</v>
+        <v>0.0113</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3237</v>
+        <v>0.9374</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1856030841934638</v>
+        <v>0.3485507775861378</v>
       </c>
     </row>
     <row r="24">
@@ -1006,22 +1006,97 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1039</v>
+        <v>-0.1041</v>
       </c>
       <c r="C24" t="n">
         <v>0.0065</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1058</v>
+        <v>-0.1059</v>
       </c>
       <c r="E24" t="n">
         <v>0.0066</v>
       </c>
       <c r="F24" t="n">
-        <v>-15.9663</v>
+        <v>-16.0391</v>
       </c>
       <c r="G24" t="n">
-        <v>2.195617844741011e-57</v>
+        <v>6.812758172713022e-58</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>d_aa</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.0598</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.1001</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-13.0236</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8.988103653279595e-39</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>d_indie</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.0427</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.0538</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-7.2129</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5.477667856739737e-13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>d_unknown</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.0973</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.1273</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-19.3015</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.21533632665722e-83</v>
       </c>
     </row>
   </sheetData>
